--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/oct-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M278"/>
+  <dimension ref="A1:M279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12224,7 +12224,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2788-901-CM26</t>
+          <t>1426099-204-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12249,43 +12249,47 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>78.132.370-5</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>15010.04</v>
+        <v>929.9</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3474-576-CM26</t>
+          <t>2788-901-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12310,12 +12314,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12325,12 +12329,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
+          <t>78.132.370-5</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -12340,7 +12344,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>47402.06</v>
+        <v>15010.04</v>
       </c>
     </row>
     <row r="190">
@@ -12984,7 +12988,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1426099-204-CM26</t>
+          <t>3474-576-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13009,41 +13013,37 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>929.9</v>
+        <v>47402.06</v>
       </c>
     </row>
     <row r="201">
@@ -15329,7 +15329,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3085-679-CM26</t>
+          <t>1237853-177-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15354,27 +15354,27 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>65.320.930-4</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORPORACION DEL DEPORTE DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -15384,13 +15384,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>818.84</v>
+        <v>806.79</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1237853-177-CM26</t>
+          <t>3085-679-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15415,27 +15415,27 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>65.320.930-4</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CORPORACION DEL DEPORTE DE LA FLORIDA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>806.79</v>
+        <v>818.84</v>
       </c>
     </row>
     <row r="239">
@@ -15886,7 +15886,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2755-452-CM26</t>
+          <t>1490610-11-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15911,27 +15911,27 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>11.647.874-9</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6084.81</v>
+        <v>9388.940000000001</v>
       </c>
     </row>
     <row r="247">
@@ -16008,7 +16008,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3223-171-CM26</t>
+          <t>836-159-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16048,32 +16048,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4869.65</v>
+        <v>2202.27</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>836-159-CM26</t>
+          <t>2173-263-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16098,27 +16094,27 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -16128,13 +16124,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2202.27</v>
+        <v>16253.96</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2173-263-CM26</t>
+          <t>3223-171-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16159,37 +16155,41 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>16253.96</v>
+        <v>4869.65</v>
       </c>
     </row>
     <row r="251">
@@ -16638,7 +16638,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1490610-11-CM26</t>
+          <t>2755-452-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16663,27 +16663,27 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>NELSON GERARDO CONTRERAS GÓNGORA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>11.647.874-9</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>9388.940000000001</v>
+        <v>6084.81</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2974-323-CM26</t>
+          <t>2432-729-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16724,12 +16724,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16739,28 +16739,32 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>9659.24</v>
+        <v>29397.1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2432-729-CM26</t>
+          <t>2799-1032-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16785,47 +16789,43 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.851.313-9</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>29397.1</v>
+        <v>3307.4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2799-1032-CM26</t>
+          <t>2341-557-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16850,27 +16850,27 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16880,13 +16880,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3307.4</v>
+        <v>3782.18</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2341-557-CM26</t>
+          <t>2799-1031-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16911,27 +16911,27 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16941,13 +16941,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3782.18</v>
+        <v>824.48</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2799-1031-CM26</t>
+          <t>2974-323-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16972,27 +16972,27 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -17002,7 +17002,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>824.48</v>
+        <v>9659.24</v>
       </c>
     </row>
     <row r="264">
@@ -17069,7 +17069,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2287-820-CM26</t>
+          <t>539119-3437-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17109,12 +17109,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17128,13 +17128,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1451.79</v>
+        <v>5109.29</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>539119-3437-CM26</t>
+          <t>2287-820-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17159,12 +17159,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>5109.29</v>
+        <v>1451.79</v>
       </c>
     </row>
     <row r="267">
@@ -17752,7 +17752,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1134432-701-CM26</t>
+          <t>1261592-1450-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17777,32 +17777,32 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>OSCAR ARMANDO ZÚÑIGA VALENZUELA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>10.020.938-1</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>36479.66</v>
+        <v>20393.91</v>
       </c>
     </row>
     <row r="277">
@@ -17882,7 +17882,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1261592-1450-CM26</t>
+          <t>1134432-701-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17907,32 +17907,32 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>OSCAR ARMANDO ZÚÑIGA VALENZUELA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>10.020.938-1</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -17941,7 +17941,72 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>20393.91</v>
+        <v>36479.66</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>3115-217-CM26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>61.102.119-4</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>GRUPO GMSE  NEGOCIOS SPA</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>77.512.806-2</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>3605.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/oct-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/oct-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M279"/>
+  <dimension ref="A1:M288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2144,7 +2144,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3191-5198-CM26</t>
+          <t>2297-1274-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2169,17 +2169,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>817.28</v>
+        <v>2713.06</v>
       </c>
     </row>
     <row r="29">
@@ -2274,7 +2274,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2297-1274-CM26</t>
+          <t>3191-5198-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2713.06</v>
+        <v>817.28</v>
       </c>
     </row>
     <row r="31">
@@ -3989,7 +3989,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1432083-2438-CM26</t>
+          <t>4494-771-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4014,27 +4014,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>INGENIERIA INDUSTRIAL CABEZAS Y MORALES SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.156.518-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -4044,13 +4044,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2784.76</v>
+        <v>3634.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4494-771-CM26</t>
+          <t>1432083-2438-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4075,27 +4075,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>INGENIERIA INDUSTRIAL CABEZAS Y MORALES SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.156.518-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3634.2</v>
+        <v>2784.76</v>
       </c>
     </row>
     <row r="59">
@@ -4737,7 +4737,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1336-171-CM26</t>
+          <t>1233616-1844-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4757,48 +4757,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1903.06</v>
+        <v>1211.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1233616-1844-CM26</t>
+          <t>3756-707-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4818,52 +4822,48 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1211.34</v>
+        <v>6246.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3756-707-CM26</t>
+          <t>3709-1108-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4918,13 +4918,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6246.74</v>
+        <v>763.25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3709-1108-CM26</t>
+          <t>1336-171-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4944,32 +4944,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4979,13 +4979,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>763.25</v>
+        <v>1903.06</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5526-61-CM26</t>
+          <t>1295444-59-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5010,27 +5010,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.942.400-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SICMER SERVICIOS DE INGENIERÍA, CONSTRUCCIÓN Y MERCADO SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.066.574-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5040,13 +5040,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>46227.05</v>
+        <v>3354.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1295444-59-CM26</t>
+          <t>2408-997-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>70.942.400-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>3354.98</v>
+        <v>1972.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2408-997-CM26</t>
+          <t>5178-4410-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5132,43 +5132,47 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>77.795.374-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1972.97</v>
+        <v>15809.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5178-4410-CM26</t>
+          <t>796290-99-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5193,47 +5197,47 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>77.795.374-5</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>15809.16</v>
+        <v>3037.63</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>796290-99-CM26</t>
+          <t>1432083-2486-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5253,52 +5257,48 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3037.63</v>
+        <v>3470.01</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1432083-2486-CM26</t>
+          <t>5526-61-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5318,32 +5318,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>SICMER SERVICIOS DE INGENIERÍA, CONSTRUCCIÓN Y MERCADO SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.066.574-4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3470.01</v>
+        <v>46227.05</v>
       </c>
     </row>
     <row r="79">
@@ -5729,7 +5729,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2408-1006-CM26</t>
+          <t>5178-4433-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5754,32 +5754,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.795.374-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8112.19</v>
+        <v>2168.62</v>
       </c>
     </row>
     <row r="86">
@@ -5916,7 +5916,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5178-4433-CM26</t>
+          <t>2408-1006-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5936,46 +5936,46 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>77.795.374-5</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2168.62</v>
+        <v>8112.19</v>
       </c>
     </row>
     <row r="89">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6355,7 +6355,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2018-201-CM26</t>
+          <t>1495203-23-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>99.590.760-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6410,13 +6410,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>919.09</v>
+        <v>1108.43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5067-2407-CM26</t>
+          <t>1426103-95-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6441,47 +6441,43 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4620.66</v>
+        <v>1208.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5520-6281-CM26</t>
+          <t>5067-2407-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6501,17 +6497,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6521,12 +6517,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6540,13 +6536,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>18204.05</v>
+        <v>4620.66</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1426103-95-CM26</t>
+          <t>5520-6281-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6566,42 +6562,46 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>77.638.992-7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1208.6</v>
+        <v>18204.05</v>
       </c>
     </row>
     <row r="99">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7050,7 +7050,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1495203-23-CM26</t>
+          <t>1495203-22-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7090,22 +7090,26 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1108.43</v>
+        <v>8862.85</v>
       </c>
     </row>
     <row r="107">
@@ -7176,7 +7180,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1495203-22-CM26</t>
+          <t>1490608-19-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7196,7 +7200,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7211,37 +7215,37 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>8862.85</v>
+        <v>925.83</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>761391-1258-CM26</t>
+          <t>2018-201-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7266,12 +7270,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.103.032-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7281,32 +7285,28 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y PRODUCTORA PRODQUIM LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.590.760-7</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>6900.26</v>
+        <v>919.09</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>924-405-CM26</t>
+          <t>761391-1261-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.103.032-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7346,28 +7346,32 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>77.685.821-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4234.84</v>
+        <v>6534.15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1432083-2434-CM26</t>
+          <t>924-405-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7387,32 +7391,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7422,13 +7426,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1204.17</v>
+        <v>4234.84</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1490608-19-CM26</t>
+          <t>1432083-2434-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7453,41 +7457,37 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>925.83</v>
+        <v>1204.17</v>
       </c>
     </row>
     <row r="113">
@@ -7875,7 +7875,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>968695-173-CM26</t>
+          <t>761391-1258-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7895,17 +7895,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.980.900-9</t>
+          <t>61.103.032-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7915,28 +7915,32 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+          <t>77.685.821-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>987.42</v>
+        <v>6900.26</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>761391-1259-CM26</t>
+          <t>968695-173-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7956,17 +7960,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.103.032-0</t>
+          <t>61.980.900-9</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7976,32 +7980,28 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>PROYECTOS &amp; REMODELACIONES C&amp;O SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.685.821-8</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1377.37</v>
+        <v>987.42</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>761391-1260-CM26</t>
+          <t>761391-1259-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8060,13 +8060,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>20327.78</v>
+        <v>1377.37</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>761391-1261-CM26</t>
+          <t>761391-1260-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6534.15</v>
+        <v>20327.78</v>
       </c>
     </row>
     <row r="123">
@@ -8196,7 +8196,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3132-406-CM26</t>
+          <t>3608-557-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8221,27 +8221,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.950.800-9</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>8677.379999999999</v>
+        <v>2560.88</v>
       </c>
     </row>
     <row r="125">
@@ -8509,7 +8509,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4020-919-CM26</t>
+          <t>377-457-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8529,52 +8529,48 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>7469.54</v>
+        <v>2787.8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1027-100-CM26</t>
+          <t>4020-919-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8599,43 +8595,47 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>BLOOMBERRY COMERCIAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.330.742-5</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>35782.93</v>
+        <v>7469.54</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1027-99-CM26</t>
+          <t>1027-100-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.330.742-5</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>29962.4</v>
+        <v>35782.93</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3608-557-CM26</t>
+          <t>1027-99-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8721,17 +8721,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2560.88</v>
+        <v>29962.4</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2345-529-CM26</t>
+          <t>3132-406-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8782,47 +8782,43 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>61.950.800-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>FERRETERIA  Y COMERCIAL MFS  SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.352.453-K</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4910.25</v>
+        <v>8677.379999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>377-457-CM26</t>
+          <t>3334-485-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8847,27 +8843,27 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8877,13 +8873,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2787.8</v>
+        <v>1824.02</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1495209-25-CM26</t>
+          <t>2432-694-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8908,47 +8904,43 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.950.108-8</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3107.19</v>
+        <v>2050.55</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2548-562-CM26</t>
+          <t>2345-529-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8973,27 +8965,27 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>FERRETERIA  Y COMERCIAL MFS  SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.352.453-K</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -9007,13 +8999,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>20529.12</v>
+        <v>4910.25</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1036-259-CM26</t>
+          <t>552975-580-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9038,27 +9030,27 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.070.301-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9072,13 +9064,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3735.56</v>
+        <v>6772.67</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>634-669-CM26</t>
+          <t>1036-259-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9103,47 +9095,47 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>33473.22</v>
+        <v>3735.56</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2432-694-CM26</t>
+          <t>634-669-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9168,12 +9160,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9183,28 +9175,32 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y DISTRIBUIDORA BULNES 78 SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.950.108-8</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2050.55</v>
+        <v>33473.22</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>552975-580-CM26</t>
+          <t>2548-562-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9229,41 +9225,41 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.070.301-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORP DE DESARROLLO SOCIAL DE PROVIDENCIA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>6772.67</v>
+        <v>20529.12</v>
       </c>
     </row>
     <row r="141">
@@ -9350,7 +9346,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9391,7 +9387,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3334-485-CM26</t>
+          <t>1495209-25-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9411,17 +9407,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9431,22 +9427,26 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1824.02</v>
+        <v>3107.19</v>
       </c>
     </row>
     <row r="144">
@@ -9517,7 +9517,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2432-700-CM26</t>
+          <t>2291-1632-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9542,41 +9542,37 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.099.725-0</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>8713.25</v>
+        <v>5911.06</v>
       </c>
     </row>
     <row r="146">
@@ -9899,7 +9895,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2291-1632-CM26</t>
+          <t>2432-700-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9924,37 +9920,41 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.099.725-0</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5911.06</v>
+        <v>8713.25</v>
       </c>
     </row>
     <row r="152">
@@ -10021,7 +10021,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1174300-83-CM26</t>
+          <t>3438-212-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10046,43 +10046,47 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>65.196.535-7</t>
+          <t>61.101.022-2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>766.89</v>
+        <v>3822.87</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1495209-27-CM26</t>
+          <t>1174300-83-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10107,47 +10111,43 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.196.535-7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.750.890-3</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5511.2</v>
+        <v>766.89</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>529318-173-CM26</t>
+          <t>1495209-27-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10172,43 +10172,47 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.724.952-7</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1217.41</v>
+        <v>5511.2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1213444-470-CM26</t>
+          <t>529318-173-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10228,52 +10232,48 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.724.952-7</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3438.59</v>
+        <v>1217.41</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1495207-14-CM26</t>
+          <t>1213444-470-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10293,37 +10293,37 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIAL TREBOL LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.601.801-5</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10332,13 +10332,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>824.6900000000001</v>
+        <v>3438.59</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2389-608-CM26</t>
+          <t>1495207-14-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10358,37 +10358,37 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>COMERCIAL TREBOL LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>77.601.801-5</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10397,13 +10397,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>14275.44</v>
+        <v>824.6900000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3438-212-CM26</t>
+          <t>2389-608-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10428,32 +10428,32 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.101.022-2</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3822.87</v>
+        <v>14275.44</v>
       </c>
     </row>
     <row r="160">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10716,7 +10716,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2408-1047-CM26</t>
+          <t>838104-939-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>INVERSIONES CHILE LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.795.374-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10775,13 +10775,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>35361.71</v>
+        <v>1778.78</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>838104-939-CM26</t>
+          <t>1860-92-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10806,47 +10806,43 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1778.78</v>
+        <v>5218.88</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1860-92-CM26</t>
+          <t>848-238-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10871,17 +10867,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10901,13 +10897,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>5218.88</v>
+        <v>1465.15</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>848-238-CM26</t>
+          <t>2291-1643-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10932,12 +10928,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10947,28 +10943,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1465.15</v>
+        <v>4760.93</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2291-1643-CM26</t>
+          <t>4809-83-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10993,41 +10993,37 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.330.742-5</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4760.93</v>
+        <v>71665.61</v>
       </c>
     </row>
     <row r="169">
@@ -11155,7 +11151,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4809-83-CM26</t>
+          <t>4809-82-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11195,12 +11191,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>BLOOMBERRY COMERCIAL SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.330.742-5</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -11210,13 +11206,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>71665.61</v>
+        <v>53462.72</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3697-891-CM26</t>
+          <t>2408-1047-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11241,43 +11237,47 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>INVERSIONES CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>77.795.374-5</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1515.66</v>
+        <v>35361.71</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4451-666-CM26</t>
+          <t>4809-81-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11302,17 +11302,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11332,13 +11332,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4405.69</v>
+        <v>52596.5</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4809-82-CM26</t>
+          <t>4451-666-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11363,17 +11363,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>53462.72</v>
+        <v>4405.69</v>
       </c>
     </row>
     <row r="175">
@@ -11720,7 +11720,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>721-277-CM26</t>
+          <t>3697-891-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11745,47 +11745,43 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>885.5700000000001</v>
+        <v>1515.66</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4809-80-CM26</t>
+          <t>721-277-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11810,43 +11806,47 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>62693.13</v>
+        <v>885.5700000000001</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4809-81-CM26</t>
+          <t>4809-80-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>52596.5</v>
+        <v>62693.13</v>
       </c>
     </row>
     <row r="183">
@@ -12289,7 +12289,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2788-901-CM26</t>
+          <t>3474-576-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12314,12 +12314,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.072.600-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAINE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12329,12 +12329,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
+          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>78.132.370-5</t>
+          <t>76.099.725-0</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>15010.04</v>
+        <v>47402.06</v>
       </c>
     </row>
     <row r="190">
@@ -12415,7 +12415,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2098-2427-CM26</t>
+          <t>1655-361-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12435,32 +12435,32 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.602.211-3</t>
+          <t>61.608.605-7</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIAL H&amp;H LIMITADA</t>
+          <t>Lars Christian</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.219.192-k</t>
+          <t>78.725.520-5</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>10348.84</v>
+        <v>3032.35</v>
       </c>
     </row>
     <row r="192">
@@ -12667,7 +12667,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1655-361-CM26</t>
+          <t>2098-2427-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12687,32 +12687,32 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.608.605-7</t>
+          <t>61.602.211-3</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLI CENTRAL DIRECCION DE ATENCION PRIMARIA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Lars Christian</t>
+          <t>COMERCIAL H&amp;H LIMITADA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>78.725.520-5</t>
+          <t>76.219.192-k</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3032.35</v>
+        <v>10348.84</v>
       </c>
     </row>
     <row r="196">
@@ -12793,7 +12793,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1134432-711-CM26</t>
+          <t>2788-901-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12818,47 +12818,43 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.072.600-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE PAINE</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>SOC FLORENTINO GARCIA Y CIA LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.132.370-5</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>13036.75</v>
+        <v>15010.04</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3734-719-CM26</t>
+          <t>1134432-711-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12883,27 +12879,27 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -12917,13 +12913,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>15961.41</v>
+        <v>13036.75</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1134432-710-CM26</t>
+          <t>3734-719-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12948,17 +12944,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12982,13 +12978,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>10659.96</v>
+        <v>15961.41</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3474-576-CM26</t>
+          <t>1134432-710-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13013,43 +13009,47 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA LA MAULINA LTDA.</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>76.099.725-0</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>47402.06</v>
+        <v>10659.96</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1490609-41-CM26</t>
+          <t>1490609-23-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13089,28 +13089,32 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1145.05</v>
+        <v>2901.58</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5684-596-CM26</t>
+          <t>1490609-41-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13135,27 +13139,27 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -13165,7 +13169,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1399.53</v>
+        <v>1145.05</v>
       </c>
     </row>
     <row r="203">
@@ -13358,7 +13362,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1490609-21-CM26</t>
+          <t>1490609-17-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13417,13 +13421,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1514.79</v>
+        <v>2225.33</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1490609-23-CM26</t>
+          <t>5684-596-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13448,41 +13452,37 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2901.58</v>
+        <v>1399.53</v>
       </c>
     </row>
     <row r="208">
@@ -13553,7 +13553,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1490609-17-CM26</t>
+          <t>1490609-27-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13612,13 +13612,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2225.33</v>
+        <v>8525.75</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1490609-29-CM26</t>
+          <t>1490609-21-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13677,7 +13677,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2287.59</v>
+        <v>1514.79</v>
       </c>
     </row>
     <row r="211">
@@ -14069,7 +14069,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1490609-27-CM26</t>
+          <t>1490609-29-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>8525.75</v>
+        <v>2287.59</v>
       </c>
     </row>
     <row r="218">
@@ -14260,7 +14260,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3232-728-CM26</t>
+          <t>1030177-135-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14285,47 +14285,43 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>NELCO SPA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.094.046-K</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.882.403-7</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>25156.32</v>
+        <v>3008.92</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1030177-135-CM26</t>
+          <t>2291-1655-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14350,43 +14346,47 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3008.92</v>
+        <v>1028.47</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2291-1655-CM26</t>
+          <t>3232-728-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14411,32 +14411,32 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>NELCO SPA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.094.046-K</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1028.47</v>
+        <v>25156.32</v>
       </c>
     </row>
     <row r="223">
@@ -14638,7 +14638,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2785-736-CM26</t>
+          <t>539119-3370-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14663,41 +14663,37 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1302.31</v>
+        <v>788.14</v>
       </c>
     </row>
     <row r="227">
@@ -14723,7 +14719,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14784,7 +14780,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -14825,7 +14821,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3217-161-CM26</t>
+          <t>2785-736-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14850,43 +14846,47 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Comercial Disaferco Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.127.832-0</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6624.19</v>
+        <v>1302.31</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>539119-3370-CM26</t>
+          <t>3217-161-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14911,27 +14911,27 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Comercial Disaferco Limitada</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.127.832-0</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>788.14</v>
+        <v>6624.19</v>
       </c>
     </row>
     <row r="231">
@@ -15138,7 +15138,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2345-553-CM26</t>
+          <t>2287-817-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15163,12 +15163,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15178,28 +15178,32 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>7233.75</v>
+        <v>2543.05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>529318-180-CM26</t>
+          <t>2345-553-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15224,47 +15228,43 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA PETCH LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.317.833-1</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>7637.58</v>
+        <v>7233.75</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>847-257-CM26</t>
+          <t>529318-180-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15304,17 +15304,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA PETCH LIMITADA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.317.833-1</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15323,13 +15323,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>14230.88</v>
+        <v>7637.58</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1237853-177-CM26</t>
+          <t>847-257-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15354,37 +15354,41 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>65.320.930-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>CORPORACION DEL DEPORTE DE LA FLORIDA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>COMERCIAL EL TORO SPA</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>76.209.677-3</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>806.79</v>
+        <v>14230.88</v>
       </c>
     </row>
     <row r="238">
@@ -15573,7 +15577,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2548-687-CM26</t>
+          <t>1173463-126-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15598,47 +15602,43 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.969.000-1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>78.610.360-6</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>4896.54</v>
+        <v>3499.6</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3085-683-CM26</t>
+          <t>2548-687-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15663,43 +15663,47 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.102.023-6</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2537.98</v>
+        <v>4896.54</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2287-817-CM26</t>
+          <t>1237853-177-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15724,12 +15728,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>65.320.930-4</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>CORPORACION DEL DEPORTE DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15739,26 +15743,22 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2543.05</v>
+        <v>806.79</v>
       </c>
     </row>
     <row r="244">
@@ -15825,7 +15825,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1173463-126-CM26</t>
+          <t>3223-171-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.969.000-1</t>
+          <t>61.102.019-8</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15865,28 +15865,32 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>3499.6</v>
+        <v>4869.65</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1490610-11-CM26</t>
+          <t>3085-683-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15911,27 +15915,27 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.102.023-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15941,13 +15945,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>9388.940000000001</v>
+        <v>2537.98</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>799512-1136-CM26</t>
+          <t>1495208-34-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15972,43 +15976,47 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>70.859.400-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>QUIMICA PASSOL S.A.</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>76.724.952-7</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1902.33</v>
+        <v>785.37</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>836-159-CM26</t>
+          <t>799512-1136-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16033,12 +16041,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>70.859.400-8</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16048,12 +16056,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
+          <t xml:space="preserve">DISTRIBUIDORA VECTOR SPA </t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>78.610.360-6</t>
+          <t>76.724.952-7</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -16063,13 +16071,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2202.27</v>
+        <v>1902.33</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2173-263-CM26</t>
+          <t>836-159-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16094,27 +16102,27 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL E INDUSTRIAL NOVA SEGURI DAD LIMITADA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>78.610.360-6</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -16124,13 +16132,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>16253.96</v>
+        <v>2202.27</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3223-171-CM26</t>
+          <t>2173-263-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16155,41 +16163,37 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.102.019-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4869.65</v>
+        <v>16253.96</v>
       </c>
     </row>
     <row r="251">
@@ -16386,7 +16390,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>761391-1295-CM26</t>
+          <t>1490610-11-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16411,47 +16415,43 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.103.032-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>9177.120000000001</v>
+        <v>9388.940000000001</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1495208-31-CM26</t>
+          <t>761391-1295-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16476,43 +16476,47 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.103.032-0</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1652.81</v>
+        <v>9177.120000000001</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1495208-33-CM26</t>
+          <t>1495208-31-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16552,12 +16556,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Comercial IBL SpA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16567,13 +16571,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2001.75</v>
+        <v>1652.81</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1495208-34-CM26</t>
+          <t>1495208-33-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16613,26 +16617,22 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>QUIMICA PASSOL S.A.</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>84.634.200-1</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.452.485-3</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>785.37</v>
+        <v>2001.75</v>
       </c>
     </row>
     <row r="258">
@@ -16699,7 +16699,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2432-729-CM26</t>
+          <t>1301-97-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16724,47 +16724,43 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>29397.1</v>
+        <v>1296.82</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2799-1032-CM26</t>
+          <t>2432-729-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16789,43 +16785,47 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>3307.4</v>
+        <v>29397.1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2341-557-CM26</t>
+          <t>2799-1032-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16850,27 +16850,27 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16880,13 +16880,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3782.18</v>
+        <v>3307.4</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2799-1031-CM26</t>
+          <t>2341-557-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16911,27 +16911,27 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>FERRETERIA LAS RASTRAS SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.851.313-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16941,13 +16941,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>824.48</v>
+        <v>3782.18</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2974-323-CM26</t>
+          <t>2799-1031-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16972,27 +16972,27 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>FERRETERIA LAS RASTRAS SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.851.313-9</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -17002,7 +17002,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>9659.24</v>
+        <v>824.48</v>
       </c>
     </row>
     <row r="264">
@@ -17069,7 +17069,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>539119-3437-CM26</t>
+          <t>2974-323-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17109,32 +17109,28 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5109.29</v>
+        <v>9659.24</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2287-820-CM26</t>
+          <t>539119-3437-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17159,12 +17155,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.253.700-9</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17174,12 +17170,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17193,13 +17189,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1451.79</v>
+        <v>5109.29</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1422051-363-CM26</t>
+          <t>2287-820-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17224,12 +17220,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>69.253.700-9</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACUL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17239,28 +17235,32 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>11584.96</v>
+        <v>1451.79</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>650-144-CM26</t>
+          <t>1422051-363-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17285,17 +17285,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17315,13 +17315,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3611.55</v>
+        <v>11584.96</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>955-22-CM26</t>
+          <t>650-144-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17346,27 +17346,27 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -17376,13 +17376,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3214.71</v>
+        <v>3611.55</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>847-258-CM26</t>
+          <t>955-22-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17407,27 +17407,27 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>27178.96</v>
+        <v>3214.71</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2555-190-CM26</t>
+          <t>847-258-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -17468,27 +17468,27 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -17498,13 +17498,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1459.69</v>
+        <v>27178.96</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1495208-49-CM26</t>
+          <t>3704-337-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17529,17 +17529,17 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.254.400-5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>Ilustre Municipalidad de Cabo de Hornos</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17559,13 +17559,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>879.6900000000001</v>
+        <v>2164.88</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2555-191-CM26</t>
+          <t>2436-1430-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17590,43 +17590,47 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Treck S.A.</t>
+          <t>TECNOQUIM SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>96.542.490-3</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr"/>
+          <t>76.378.846-6</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2652.71</v>
+        <v>6528.83</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2436-1430-CM26</t>
+          <t>1495208-49-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17651,47 +17655,43 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>TECNOQUIM SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.378.846-6</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>6528.83</v>
+        <v>879.6900000000001</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3704-337-CM26</t>
+          <t>2555-191-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17716,27 +17716,27 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.254.400-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabo de Hornos</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Treck S.A.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.542.490-3</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17746,13 +17746,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2164.88</v>
+        <v>2652.71</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1261592-1450-CM26</t>
+          <t>3512-917-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -17777,27 +17777,27 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -17811,13 +17811,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>20393.91</v>
+        <v>4034.59</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1658-2484-CM26</t>
+          <t>979-1446-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -17842,47 +17842,43 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>54638.1</v>
+        <v>3281.72</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1134432-701-CM26</t>
+          <t>3712-699-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17897,7 +17893,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -17907,105 +17903,662 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>OSCAR ARMANDO ZÚÑIGA VALENZUELA</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>10.020.938-1</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>36479.66</v>
+        <v>1201.89</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
+          <t>2555-190-CM26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Treck S.A.</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>96.542.490-3</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>1459.69</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1962-702-CM26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>61.004.012-8</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>844.14</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1658-2484-CM26</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="n">
+        <v>54638.1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>1134432-701-CM26</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>OSCAR ARMANDO ZÚÑIGA VALENZUELA</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>10.020.938-1</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>36479.66</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>1134432-714-CM26</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="n">
+        <v>1254.92</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1261592-1444-CM26</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="n">
+        <v>3712.47</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>1261592-1450-CM26</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="n">
+        <v>20393.91</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>3016-596-CM26</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>69.090.500-0</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOLOL</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>78.456.070-8</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>2906.97</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>1346280-15-CM26</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="n">
+        <v>20129.56</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
           <t>3115-217-CM26</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2239-9-LR23</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>oct-2026</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
         <is>
           <t>61.102.119-4</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="G288" t="inlineStr">
         <is>
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="H288" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
+      <c r="I288" t="inlineStr">
         <is>
           <t>GRUPO GMSE  NEGOCIOS SPA</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr">
+      <c r="J288" t="inlineStr">
         <is>
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="K288" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M279" s="2" t="n">
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="n">
         <v>3605.25</v>
       </c>
     </row>
